--- a/Översikt HALMSTAD.xlsx
+++ b/Översikt HALMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45594</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>45099</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45447</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45820</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>44974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45442</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45352</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>45168</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45168</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>44767</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>45168</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45356</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>45734</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45168</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>45168</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>44734</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45397</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>45352</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45442</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44595</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44538</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>44537</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>45120</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45168</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45894</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>46175</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>46069</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>45042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45264</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45168</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45874</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>46153</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>44537</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>44537</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>44656</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>44897</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45306</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45168</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45315</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>44482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45168</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45715</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>46149</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>45692</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>45035</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>44715</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45441</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>46069</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45154</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>46162</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>46176</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>46178</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>45925</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>46057</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>46057</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>46182</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>46106</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45615</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>46057</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>45122</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>45168</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>45441</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>45812</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45839</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>44621</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>45692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44699</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>45082</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45050</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>45029</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>45874</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45883</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45915</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>46141</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>44756</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44705</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>44677</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44796</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44873</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>44470</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>44516</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>44537</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>44470</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>44536</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44872</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>44538</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>44593</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>44628</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>44649</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>44474</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>44760</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44760</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>44470</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>44677</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>44865</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44538</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>44537</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44579</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44722</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>44494</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>44593</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44544</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44875</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45079</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>45363</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>45630</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45610</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>45183</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>45358</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45265</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45275</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45091</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>45196</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>45279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>44461</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44845</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>45733</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45775</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>45240</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45561</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45169</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>44482</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45168</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>45660</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45168</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>45168</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45168</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>44823</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45734</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>44691</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>45239</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>44594</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>45329</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>44687</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>45168</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>45231</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>45260</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>44827</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>45257</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>45258</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>45302</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>45065</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>45000</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45356</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>45259</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45680</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45015</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>45015</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>45015</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45168</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>44952</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>45275</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>44885</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>44622</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44885</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45257</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44742</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45240</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45415</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>45488</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44830</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45660</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>45735</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>45805</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>45531</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45323</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>45800</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45714</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>45692</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>45251</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>45681</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>45681</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>45800</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45401</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>45750</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>45769</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>45257</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>45831</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45408</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45356</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45316</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45883</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>45215</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>45894</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45589</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45168</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45170</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45729</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45740</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45091</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>44662</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44711</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45259</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>45488</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>45335</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45917</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45916</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45917</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45715</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45279</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45923</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45562</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>45562</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45167</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>45636</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45636</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45926</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45931</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45931</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45555</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45889</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>45938</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45183</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45279</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>45168</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>45268</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45209</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45050</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45329</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>45952</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>44712</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45959</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>46153</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45264</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45258</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>46105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44628</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44880</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44897</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45967</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45758</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45727</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44557</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45476</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45476</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45607</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45981</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45217</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45348</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45699</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45988</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45323</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45897</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>44607</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45988</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44518</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>44520</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45117</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45537</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>46162</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>46162</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>44610</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44753</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44721</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>46162</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>46162</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44742</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>44959</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45170</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45159</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>46167</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>46167</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>46167</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>46167</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>44802</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>46006</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>46008</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>46007</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>46168</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45316</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>46008</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>44595</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>46013</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44917</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45126</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>45259</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45589</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45973</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>44852</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45170</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>46031</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46173</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45485</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45924</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>46034</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>46034</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>46173</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44974</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>44775</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>44910</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44571</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>46176</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>46176</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>46050</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>45168</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45588</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>46057</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46057</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>46057</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>46178</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45156</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>44868</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>46178</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>46059</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>44938</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>46059</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>46062</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45006</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>45660</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>46182</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>46066</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>46066</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45217</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45217</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>45321</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45267</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45267</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>46181</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45562</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>46079</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>45627</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27865,7 +27865,7 @@
         <v>45967</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>45895</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>45973</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>46188</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>46188</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>46188</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>46188</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>46188</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45154</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>46188</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>46188</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>46188</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45386</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44482</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>44482</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>44642</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>44722</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44537</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>44712</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>46188</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45230</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>46188</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45239</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45239</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>46188</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>44461</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>46090</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46092</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46059</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>46189</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45589</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>44806</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>46196</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45168</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45168</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         <v>46106</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>46105</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>46105</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>46105</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>44482</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>46107</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44922</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>44964</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44964</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>46197</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45168</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>46121</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>46121</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45531</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>46121</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>46128</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44713</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>46085</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45404</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45600</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>44466</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44974</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45632</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45826</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>44964</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45169</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45203</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45168</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>46205</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45099</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>46206</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>46253</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>45049</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>46253</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45632</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>46210</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>46210</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>45238</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45099</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>44827</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45561</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>46210</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>46210</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>46210</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>46210</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>46210</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>46210</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>46254</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>45712</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>46254</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>44974</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>45450</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>46258</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>46259</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>46258</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>46259</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>46258</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>45429</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>45306</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44470</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>45561</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45216</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>44964</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>46265</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>46265</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>46265</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>46260</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>46265</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45733</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>44775</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>45090</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45267</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>45194</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>45229</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>44886</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45712</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>45071</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>46273</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>46265</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45443</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45583</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>46027</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>45555</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>46274</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45677</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>46274</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>46276</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>46276</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45747</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45792</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45694</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>44677</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45226</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45562</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45797</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>45716</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>45316</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45627</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>45735</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45330</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>45359</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45817</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45642</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45824</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45831</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45831</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45831</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45831</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45831</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45561</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45841</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45841</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45708</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45793</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45846</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45681</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45854</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45856</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45750</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45741</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45493</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>45172</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44917</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>44917</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45079</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45000</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>44917</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>45736</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45229</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44879</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>44879</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>44917</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45581</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>45082</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40320,7 +40320,7 @@
         <v>45001</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40393,7 +40393,7 @@
         <v>44580</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>44817</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45311</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45266</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45642</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45692</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45006</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>45278</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>45611</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45159</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>44621</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45099</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>45750</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>45357</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45797</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>44699</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45068</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45581</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45579</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45299</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>45874</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>45874</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>45874</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45876</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>45880</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44132</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>44767</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>44592</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45171</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>44469</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>45672</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>45516</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>45750</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45636</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45734</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45729</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>45716</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>46163</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>46244</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>46212</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>

--- a/Översikt HALMSTAD.xlsx
+++ b/Översikt HALMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45594</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>45099</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45447</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45820</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>44974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45442</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45352</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>45824</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44767</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45168</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45168</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>45168</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45356</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>45734</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45168</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44734</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>46288</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>45168</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45351</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>45397</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45442</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>45120</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>46069</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45894</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45168</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>46175</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>45874</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>45264</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45042</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>45168</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44537</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>44537</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44656</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>45883</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>44897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>46057</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>46057</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45715</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45441</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>45168</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45168</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>46106</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45315</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45812</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>45615</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>46149</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>45839</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>46162</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>46069</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>45035</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46176</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>45925</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>46178</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>46182</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>45050</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>45082</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>45029</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>44621</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>45122</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44699</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>45874</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>45692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>46057</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>45168</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45154</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45306</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>44715</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45441</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45915</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>46141</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>44872</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>44677</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>44796</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>44711</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44873</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>44470</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44516</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44537</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44470</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>44536</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44872</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44538</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44593</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>44628</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44649</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44474</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44760</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44760</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44470</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>44677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>44865</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>44538</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44537</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>44579</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>44722</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44494</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44593</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44544</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45735</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>45217</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>44922</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45230</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>44775</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45259</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45321</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45265</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>44952</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>44802</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45531</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45306</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45694</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45627</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>45562</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44677</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45537</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>45973</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45316</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>44886</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>45716</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>45226</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>45168</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45476</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45476</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45797</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>46034</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>46031</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45485</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45488</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45800</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>45750</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>45800</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44537</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>45769</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45805</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>45714</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44885</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45894</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45561</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45194</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45740</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45699</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>46050</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44571</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>44917</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>44610</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>46057</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>46057</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>46057</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>44938</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>46062</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45916</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>46059</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>46059</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45917</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45917</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45715</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>46066</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>46066</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44711</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45923</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45926</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45240</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44687</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>46079</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45215</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45895</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45967</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>45931</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>45973</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45931</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45330</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45735</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45359</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44974</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>45589</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45627</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>46090</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45889</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45938</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44642</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44974</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>46092</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45090</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>44607</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>46105</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46105</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45006</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>44742</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>46105</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45168</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>46106</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45562</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45952</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>46107</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45589</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>45712</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45275</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45260</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45959</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>46121</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>46121</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>46121</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44959</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45967</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45000</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45356</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>45817</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>44964</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45015</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>46128</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>45610</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45159</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44880</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>44897</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45981</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>44753</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45729</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45988</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45117</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45168</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45168</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44775</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44823</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45692</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45488</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45733</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45168</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45642</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45831</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45091</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>46006</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>44482</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>46008</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>46008</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>44827</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>46007</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>45826</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45229</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45660</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45660</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45323</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>46013</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45824</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>44885</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45264</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>45154</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>45775</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>44845</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45831</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>45831</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>45831</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>45831</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45831</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>45167</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45561</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>45203</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>46153</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>46105</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45275</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>46162</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45561</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45015</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45015</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>44518</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45841</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>46162</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45897</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45758</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>46162</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45257</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45841</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>46162</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45356</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45846</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>46168</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>45793</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>46167</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45708</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45681</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>46167</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>46167</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45854</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45363</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>46167</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45561</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>45856</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45750</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45259</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>46034</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45741</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45924</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>46173</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>46173</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>45493</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44557</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>46176</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>46178</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>46178</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>46176</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44917</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44917</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45099</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>45001</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>46182</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>46181</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>45797</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27202,7 +27202,7 @@
         <v>45302</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44817</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>45611</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45736</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>45692</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44879</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>44879</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44917</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>45068</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45159</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>44699</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>44580</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45642</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45299</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>45156</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45311</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44621</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45000</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45006</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>45630</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45170</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45229</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>45266</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>46188</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>45278</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>46189</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>45555</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45357</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45581</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>46188</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46188</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45579</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45079</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45750</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>46188</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>46188</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>46188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>46188</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>46188</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>46188</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45588</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>46059</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45874</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>46188</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>46188</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>45581</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>45874</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>45874</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44917</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45172</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45082</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45348</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45170</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45876</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>44594</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>44628</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45880</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>46197</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>46196</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45632</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45168</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>46085</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>45660</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>46205</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45316</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45883</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45681</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45681</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45091</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>46206</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>45217</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>45217</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>44721</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45636</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>45636</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>46210</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>46210</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>45049</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>46210</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>46210</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>46210</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>46210</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>46253</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>46253</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>46210</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>46210</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44662</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45401</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45099</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>44722</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>46258</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>46258</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>46254</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>46258</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>46254</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>45209</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>45733</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>45183</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>46259</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>45531</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>44742</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45183</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>45238</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>46259</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45239</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45169</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44910</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45258</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45126</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44712</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>46265</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>46265</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>46265</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>46265</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45257</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>46265</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>46265</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45267</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>45677</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>46273</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>46274</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>46274</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45259</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>44830</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45279</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>45168</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36440,7 +36440,7 @@
         <v>44868</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45239</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45239</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45386</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>45450</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45267</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>45329</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>44482</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>44470</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>46276</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>46276</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>46260</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45429</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>45268</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>46288</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37540,7 +37540,7 @@
         <v>44875</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>44595</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37686,7 +37686,7 @@
         <v>45988</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>46027</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>45404</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>45279</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>44827</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45257</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45727</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>44806</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44691</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>45071</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44482</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44482</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>44466</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>44964</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>44964</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>45408</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45216</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45168</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>44713</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45168</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44622</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>45231</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>45267</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44852</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44974</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39531,7 +39531,7 @@
         <v>45323</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45632</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44712</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45050</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39823,7 +39823,7 @@
         <v>45099</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>44964</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45168</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>45168</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40130,7 +40130,7 @@
         <v>45169</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>45240</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>45168</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45279</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>45251</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>45196</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45335</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>45316</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>45562</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>45562</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40865,7 +40865,7 @@
         <v>45589</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40938,7 +40938,7 @@
         <v>45065</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>45079</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45168</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41162,7 +41162,7 @@
         <v>45712</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>45170</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>45258</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>44520</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41454,7 +41454,7 @@
         <v>45680</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>45329</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>45734</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41673,7 +41673,7 @@
         <v>45358</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45415</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41819,7 +41819,7 @@
         <v>45607</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>45443</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45555</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>45583</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45792</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42184,7 +42184,7 @@
         <v>45747</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>44132</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>44592</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42408,7 +42408,7 @@
         <v>45516</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44767</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45171</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44469</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45672</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>45750</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>45636</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>45734</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45729</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43070,7 +43070,7 @@
         <v>45716</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>46163</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>46212</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>46244</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>

--- a/Översikt HALMSTAD.xlsx
+++ b/Översikt HALMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45594</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>45099</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45447</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45820</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>44974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45442</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45352</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>45824</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44767</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45168</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45168</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>45168</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45356</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>45734</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45168</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44734</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>46288</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>45168</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45351</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>45397</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45442</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>45120</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>46069</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45894</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45168</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>46175</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>45874</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>45264</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45042</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>45168</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44537</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>44537</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44656</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>45883</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>44897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>46057</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>46057</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45715</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45441</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>45168</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45168</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>46106</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45315</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45812</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>45615</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>46149</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>45839</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>46162</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>46069</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>45035</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46176</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>45925</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>46178</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>46182</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>45050</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>45082</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>45029</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>44621</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>45122</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44699</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>45874</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>45692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>46057</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>45168</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45154</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45306</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>44715</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45441</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45915</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>46141</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>44872</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>44677</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>44796</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>44711</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44873</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>44470</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44516</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44537</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44470</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>44536</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44872</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44538</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44593</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>44628</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44649</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44474</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44760</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44760</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44470</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>44677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>44865</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>44538</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44537</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>44579</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>44722</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44494</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44593</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44544</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45735</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>45217</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>44922</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45230</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>44775</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45259</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45321</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45265</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>44952</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>44802</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45531</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45306</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45694</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45627</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>45562</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44677</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45537</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>45973</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45316</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>44886</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>45716</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>45226</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>45168</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45476</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45476</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45797</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>46034</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>46031</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45485</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45488</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45800</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>45750</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>45800</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44537</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>45769</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45805</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>45714</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44885</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45894</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45561</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45194</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45740</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45699</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>46050</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44571</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>44917</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>44610</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>46057</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>46057</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>46057</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>44938</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>46062</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45916</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>46059</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>46059</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45917</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45917</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45715</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>46066</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>46066</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44711</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45923</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45926</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45240</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44687</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>46079</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45215</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45895</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45967</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>45931</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>45973</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45931</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45330</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45735</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45359</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44974</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>45589</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45627</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>46090</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45889</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45938</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44642</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44974</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>46092</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45090</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>44607</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>46105</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46105</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45006</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>44742</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>46105</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45168</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>46106</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45562</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45952</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>46107</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45589</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>45712</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45275</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45260</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45959</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>46121</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>46121</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>46121</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44959</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45967</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45000</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45356</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>45817</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>44964</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45015</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>46128</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>45610</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45159</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44880</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>44897</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45981</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>44753</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45729</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45988</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45117</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45168</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45168</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44775</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44823</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45692</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45488</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45733</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45168</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45642</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45831</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45091</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>46006</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>44482</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>46008</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>46008</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>44827</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>46007</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>45826</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45229</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45660</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45660</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45323</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>46013</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45824</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>44885</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45264</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>45154</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>45775</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>44845</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45831</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>45831</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>45831</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>45831</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45831</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>45167</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45561</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>45203</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>46153</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>46105</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45275</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>46162</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45561</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45015</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45015</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>44518</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45841</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>46162</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45897</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45758</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>46162</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45257</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45841</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>46162</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45356</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45846</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>46168</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>45793</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>46167</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45708</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45681</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>46167</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>46167</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45854</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45363</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>46167</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45561</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>45856</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45750</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45259</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>46034</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45741</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45924</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>46173</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>46173</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>45493</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44557</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>46176</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>46178</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>46178</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>46176</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44917</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44917</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45099</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>45001</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>46182</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>46181</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>45797</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27202,7 +27202,7 @@
         <v>45302</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44817</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>45611</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45736</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>45692</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44879</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>44879</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44917</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>45068</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45159</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>44699</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>44580</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45642</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45299</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>45156</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45311</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44621</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45000</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45006</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>45630</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45170</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45229</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>45266</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>46188</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>45278</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>46189</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>45555</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45357</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45581</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>46188</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46188</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45579</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45079</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45750</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>46188</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>46188</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>46188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>46188</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>46188</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>46188</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45588</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>46059</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45874</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>46188</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>46188</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>45581</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>45874</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>45874</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44917</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45172</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45082</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45348</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45170</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45876</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>44594</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>44628</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45880</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>46197</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>46196</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45632</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45168</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>46085</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>45660</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>46205</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45316</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45883</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45681</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45681</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45091</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>46206</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>45217</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>45217</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>44721</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45636</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>45636</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>46210</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>46210</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>45049</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>46210</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>46210</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>46210</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>46210</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>46253</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>46253</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>46210</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>46210</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44662</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45401</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45099</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>44722</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>46258</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>46258</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>46254</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>46258</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>46254</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>45209</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>45733</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>45183</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>46259</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>45531</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>44742</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45183</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>45238</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>46259</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45239</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45169</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44910</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45258</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45126</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44712</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>46265</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>46265</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>46265</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>46265</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45257</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>46265</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>46265</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45267</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>45677</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>46273</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>46274</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>46274</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45259</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>44830</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45279</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>45168</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36440,7 +36440,7 @@
         <v>44868</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45239</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45239</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45386</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>45450</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45267</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>45329</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>44482</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>44470</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>46276</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>46276</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>46260</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45429</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>45268</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>46288</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37540,7 +37540,7 @@
         <v>44875</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>44595</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37686,7 +37686,7 @@
         <v>45988</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>46027</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>45404</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>45279</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>44827</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45257</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45727</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>44806</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44691</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>45071</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44482</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44482</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>44466</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>44964</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>44964</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>45408</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45216</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45168</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>44713</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45168</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44622</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>45231</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>45267</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44852</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44974</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39531,7 +39531,7 @@
         <v>45323</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45632</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44712</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45050</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39823,7 +39823,7 @@
         <v>45099</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>44964</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45168</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>45168</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40130,7 +40130,7 @@
         <v>45169</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>45240</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>45168</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45279</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>45251</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>45196</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45335</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>45316</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>45562</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>45562</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40865,7 +40865,7 @@
         <v>45589</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40938,7 +40938,7 @@
         <v>45065</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>45079</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45168</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41162,7 +41162,7 @@
         <v>45712</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>45170</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>45258</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>44520</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41454,7 +41454,7 @@
         <v>45680</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>45329</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>45734</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41673,7 +41673,7 @@
         <v>45358</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45415</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41819,7 +41819,7 @@
         <v>45607</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>45443</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45555</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>45583</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45792</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42184,7 +42184,7 @@
         <v>45747</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>44132</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>44592</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42408,7 +42408,7 @@
         <v>45516</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44767</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45171</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44469</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45672</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>45750</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>45636</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>45734</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45729</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43070,7 +43070,7 @@
         <v>45716</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>46163</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>46212</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>46244</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>

--- a/Översikt HALMSTAD.xlsx
+++ b/Översikt HALMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45594</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>45099</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45447</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45820</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>44974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45442</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45352</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>45168</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45824</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>44767</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45168</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>45168</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45356</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>45734</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44734</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>45168</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>46288</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45168</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>45397</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45442</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>45120</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>46069</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45168</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45894</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45874</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>46175</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>45042</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>45264</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>45168</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44537</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>44537</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44656</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44897</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45306</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45168</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>45715</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>46057</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>45315</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>44482</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>45812</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>46106</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45839</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45168</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44621</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>45692</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44699</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45082</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45050</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>45029</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>46149</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>45692</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45035</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44715</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>46069</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45874</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>46162</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>45441</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>45883</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>46176</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>46178</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>45154</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45925</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>46182</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>46057</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45615</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>46057</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45168</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>45441</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>45915</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>46141</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>44756</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>44705</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44677</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>44796</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>44873</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44516</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44537</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44536</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>44538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>44593</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>44628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>44649</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44474</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>44760</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44760</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44677</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44865</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>44538</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>44537</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44579</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44722</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>44494</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>44593</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44544</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44875</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>45279</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>45079</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45363</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>45630</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>45610</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>45183</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>45358</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>45265</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>45091</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>45196</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>45275</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>46006</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>45805</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>46008</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>46007</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>45800</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>46008</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>46013</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>45714</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>45800</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>45750</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>45894</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>45973</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>45747</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>46031</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45740</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>46034</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44845</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>45733</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>44482</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45792</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45775</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45561</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45240</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45169</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45694</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44677</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45226</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45660</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45562</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45797</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45716</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45168</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45316</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45917</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45627</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45916</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45917</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>46050</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>45715</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45168</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45168</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>45923</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>46057</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44691</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>46059</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45926</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>44823</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>46059</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45734</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45239</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>44594</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45931</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45931</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45329</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>46066</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>46066</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45889</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45938</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44687</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45231</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45735</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45168</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45330</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45359</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>46079</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45260</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45952</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45895</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>44827</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45257</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45258</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45302</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45065</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45959</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45000</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>46090</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>46092</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45817</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45967</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45259</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45015</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45015</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45015</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45356</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45680</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45168</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>44885</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44885</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>44952</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44742</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45240</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45275</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>44622</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>46106</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>46105</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45257</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>46105</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>46105</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>46107</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45642</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45981</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45488</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>44830</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45415</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45660</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45824</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45988</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45735</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>46121</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>46121</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>46121</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45531</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>46128</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45831</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45251</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45831</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45831</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45681</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45681</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45831</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45831</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45401</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45561</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45257</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45408</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>45356</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>45316</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45215</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45589</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45168</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>45170</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         <v>45841</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>45841</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>45826</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45091</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>44662</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>44711</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>45259</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         <v>45708</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>45323</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>45488</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>45793</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45846</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>45692</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45335</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45681</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45831</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45279</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45854</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>45856</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45562</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>45562</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45729</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45167</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45636</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>45636</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45750</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45741</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45555</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45183</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45279</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45168</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45493</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45268</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45172</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>44917</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>44917</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>45079</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45000</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>44917</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45736</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45209</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45229</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>44879</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>44879</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>44917</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45581</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45082</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45001</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>44580</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44817</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45311</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45266</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45642</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45692</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45050</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45329</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45006</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45278</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45611</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45159</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>44621</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45099</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45750</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45357</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>45797</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>44699</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45068</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>45581</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45579</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44712</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>45299</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>46153</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45264</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45874</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45258</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>46105</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44628</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44880</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>45874</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45874</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>44897</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>45758</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45897</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>45727</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>44557</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45876</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>46162</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>46162</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>46162</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>46162</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45476</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>45476</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>46167</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>46167</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>46167</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>46167</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45880</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45607</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>46168</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>45217</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45348</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>45699</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>46173</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45924</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>46034</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45323</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>46173</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44607</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44518</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44520</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45117</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>46176</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>46176</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45537</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>46178</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45769</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>46178</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45883</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>44610</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>46182</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>44753</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44721</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>46181</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44742</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>44959</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>46188</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>46188</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>46188</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>46188</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>46188</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45170</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>46188</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>46188</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>46188</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46188</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>46188</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45159</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>46188</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>46059</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>44802</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46189</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45316</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44595</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>46196</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44917</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>45126</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>46197</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>45259</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
         <v>45589</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>46085</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>44852</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45170</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>45485</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46205</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44974</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>46206</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>45049</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>46210</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>46210</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>46210</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>44775</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>46210</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>46210</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>46210</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>46210</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>46210</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>44910</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44571</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46258</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46259</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>46258</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>46259</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>46258</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45168</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>45588</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>46265</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>46265</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>46265</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>45156</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>44868</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>44938</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>46265</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>45006</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45660</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45217</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45217</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45321</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45267</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>45267</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45562</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>46273</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45627</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>46274</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>45677</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>46274</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>45154</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>45386</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>44482</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>44482</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>44642</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>44722</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44537</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>44712</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45230</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45239</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>45239</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>45589</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>44806</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>45168</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45168</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37743,7 +37743,7 @@
         <v>45988</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>44482</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>46276</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>44922</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>44964</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>44964</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>46288</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>46260</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45168</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45531</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>46276</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>44713</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45404</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45600</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>44974</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>45632</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>44964</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45169</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>46027</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>46254</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>46254</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45203</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45168</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>46296</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>46253</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>46296</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>46253</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
         <v>46265</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45099</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45632</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>45238</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>45099</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44827</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45561</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>45712</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>44974</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>45450</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>45429</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45306</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>45561</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>45216</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>44964</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40834,7 +40834,7 @@
         <v>45733</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>44775</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45090</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>45267</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45194</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45229</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>44886</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45712</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45071</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45443</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45583</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45555</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44132</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>44767</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44592</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45171</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>45672</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>45516</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42158,7 +42158,7 @@
         <v>45750</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>45636</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>45734</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45729</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45716</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>46163</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>46212</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>46244</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>

--- a/Översikt HALMSTAD.xlsx
+++ b/Översikt HALMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45594</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>45099</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45447</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45820</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>44974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45442</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45352</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>45730</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>45168</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45824</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>44767</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45168</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>45168</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45356</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>45734</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>44812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44734</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>45168</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>46288</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45168</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>45397</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45442</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>45120</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>46069</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45168</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45894</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45874</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>46175</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>45042</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>45264</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>45168</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44537</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>44537</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44656</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44897</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45306</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45168</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>45715</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>46057</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>45315</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>44482</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>45812</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>46106</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45839</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45168</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44621</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>45692</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44699</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45082</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45050</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>45029</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>46149</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>45692</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45035</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44715</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>46069</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45874</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>46162</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>45441</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>45883</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>46176</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>46178</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>45154</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45925</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>46182</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>46057</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45615</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>46057</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45168</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>45441</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>45915</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>46141</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>44756</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>44705</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44677</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>44796</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>44873</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44516</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44537</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44536</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>44538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>44593</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>44628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>44649</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44474</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>44760</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44760</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44677</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44865</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>44538</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>44537</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44579</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44722</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>44494</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>44593</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44544</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44875</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>45279</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>45079</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45363</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>45630</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>45610</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>45183</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>45358</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>45265</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>45091</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>45196</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>45275</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>46006</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>45805</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>46008</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>46007</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>45800</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>46008</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>46013</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>45714</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>45800</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>45750</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>45894</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>45973</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>45747</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>46031</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45740</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>46034</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44845</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>45733</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>44482</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45792</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45775</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45561</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45240</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45169</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45694</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44677</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45226</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45660</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45562</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45797</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45716</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45168</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45316</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45917</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45627</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45916</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45917</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>46050</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>45715</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45168</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45168</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>45923</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>46057</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44691</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>46059</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45926</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>44823</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>46059</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45734</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45239</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>44594</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45931</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45931</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45329</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>46066</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>46066</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45889</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45938</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44687</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45231</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45735</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45168</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45330</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45359</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>46079</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45260</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45952</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45895</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>44827</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45257</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45258</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45302</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45065</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45959</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45000</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>46090</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>46092</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45817</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45967</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45259</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45015</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45015</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45015</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45356</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45680</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45168</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>44885</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44885</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>44952</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44742</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45240</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45275</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>44622</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>46106</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>46105</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45257</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>46105</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>46105</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>46107</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45642</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45981</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45488</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>44830</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45415</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45660</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45824</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45988</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45735</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>46121</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>46121</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>46121</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45531</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>46128</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45831</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45251</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45831</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45831</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45681</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45681</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45831</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45831</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45401</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45561</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45257</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45408</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>45356</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>45316</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45215</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45589</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45168</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>45170</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         <v>45841</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>45841</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>45826</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45091</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>44662</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>44711</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>45259</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         <v>45708</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>45323</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>45488</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>45793</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45846</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>45692</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45335</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45681</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45831</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45279</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45854</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>45856</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45562</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>45562</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45729</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45167</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45636</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>45636</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45750</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45741</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45555</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45183</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45279</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45168</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45493</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45268</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45172</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>44917</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>44917</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>45079</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45000</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>44917</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45736</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45209</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45229</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>44879</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>44879</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>44917</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45581</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45082</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45001</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>44580</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44817</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45311</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45266</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45642</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45692</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45050</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45329</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45006</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45278</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45611</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45159</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>44621</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45099</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45750</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45357</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>45797</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>44699</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45068</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>45581</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45579</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44712</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>45299</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>46153</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45264</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45874</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45258</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>46105</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44628</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44880</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>45874</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45874</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>44897</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>45758</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45897</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>45727</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>44557</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45876</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>46162</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>46162</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>46162</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>46162</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45476</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>45476</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>46167</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>46167</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>46167</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>46167</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45880</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45607</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>46168</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>45217</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45348</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>45699</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>46173</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45924</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>46034</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45323</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>46173</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44607</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44518</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44520</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45117</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>46176</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>46176</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45537</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>46178</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45769</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>46178</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45883</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>44610</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>46182</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>44753</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44721</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>46181</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44742</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>44959</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>46188</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>46188</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>46188</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>46188</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>46188</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45170</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>46188</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>46188</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>46188</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46188</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>46188</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45159</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>46188</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>46059</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>44802</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46189</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45316</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44595</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>46196</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44917</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>45126</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>46197</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>45259</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
         <v>45589</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>46085</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>44852</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45170</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>45485</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46205</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44974</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>46206</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>45049</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>46210</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>46210</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>46210</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>44775</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>46210</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>46210</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>46210</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>46210</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>46210</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>44910</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44571</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46258</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46259</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>46258</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>46259</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>46258</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45168</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>45588</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>46265</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>46265</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>46265</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>45156</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>44868</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>44938</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>46265</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>45006</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45660</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45217</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45217</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45321</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45267</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>45267</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45562</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>46273</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45627</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>46274</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>45677</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>46274</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>45154</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>45386</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>44482</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>44482</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>44642</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>44722</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44537</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>44712</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45230</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45239</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>45239</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>45589</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>44806</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>45168</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45168</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37743,7 +37743,7 @@
         <v>45988</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>44482</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>46276</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>44922</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>44964</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>44964</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>46288</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>46260</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45168</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45531</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>46276</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>44713</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45404</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45600</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>44974</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>45632</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>44964</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45169</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>46027</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>46254</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>46254</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45203</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45168</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>46296</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>46253</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>46296</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>46253</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
         <v>46265</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45099</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45632</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>45238</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>45099</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44827</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45561</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>45712</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>44974</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>45450</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>45429</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45306</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>45561</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>45216</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>44964</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40834,7 +40834,7 @@
         <v>45733</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>44775</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45090</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>45267</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45194</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45229</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>44886</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45712</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45071</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45443</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45583</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45555</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44132</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>44767</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44592</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45171</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>45672</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>45516</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42158,7 +42158,7 @@
         <v>45750</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>45636</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>45734</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45729</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45716</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>46163</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>46212</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>46244</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>

--- a/Översikt HALMSTAD.xlsx
+++ b/Översikt HALMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45594</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>45099</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45447</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45820</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>44974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45442</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>45352</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>45352</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45730</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45168</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45168</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45168</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>44767</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45356</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45734</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45351</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45168</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44734</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>45168</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>46288</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45397</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45442</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44537</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44538</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>45168</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>45120</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45264</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45168</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>45042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>45894</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>46069</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>46175</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46153</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>44537</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>44537</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44656</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45306</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44715</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45035</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44482</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45883</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>45692</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45441</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44897</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45715</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>45168</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>45441</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45168</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>45168</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45812</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>45315</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>45154</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45839</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45615</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>45050</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>45082</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45029</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>44621</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>44699</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45874</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45692</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>46106</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>46057</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>46149</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>46162</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>46069</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>46176</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>45925</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>46178</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>46182</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>46057</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>46057</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>46300</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>45915</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>46141</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44756</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>44705</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>44677</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>44796</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>44873</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>44516</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>44537</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>44536</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>44760</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44538</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>44865</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>44593</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44538</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>44593</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>44628</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>44537</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44649</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>44677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>44579</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44760</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>44722</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>44494</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>44544</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>45632</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>44712</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>45050</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>45167</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45099</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45203</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44964</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45259</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>44775</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>45735</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45217</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>45168</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45168</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45169</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45275</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>45321</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45240</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>45168</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45561</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>45279</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45015</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45015</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44518</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45758</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45257</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44922</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45356</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44952</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45251</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45196</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>45265</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45230</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45335</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45883</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45316</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45562</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>45562</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45363</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44802</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45561</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45589</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45531</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>45065</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45306</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45259</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45079</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45537</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45800</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45750</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44886</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45800</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45769</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45805</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45714</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45712</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45170</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45168</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45258</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>44520</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>44557</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45680</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45476</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45476</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45894</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45485</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45488</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44537</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45329</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45734</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45358</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45740</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44885</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45415</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45607</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45561</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45194</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45699</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>44571</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45302</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45443</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45916</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44917</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>44610</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45555</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45156</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45630</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45170</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>45583</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44938</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45917</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45917</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>45555</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>45715</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45588</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45348</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45170</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44711</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45923</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45926</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>45792</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44594</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>44628</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>45747</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>45240</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>44687</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>45694</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>45627</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>45562</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>45632</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>44677</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45215</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45168</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>45316</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45716</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45931</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>45226</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45931</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44974</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>45589</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45797</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>45627</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>44642</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>45660</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44974</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45316</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45889</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>45681</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45681</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45091</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45090</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45938</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44607</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45330</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45006</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45735</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44742</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45217</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45217</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45359</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>44721</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>45168</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>45636</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45636</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45562</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45600</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45589</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45712</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45275</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>44662</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45401</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45817</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45260</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45099</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44722</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45642</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>44959</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45824</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45209</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45733</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>45183</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>45531</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45831</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>44742</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45831</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>45831</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45831</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45183</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45831</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45238</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45952</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45959</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45561</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45000</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45356</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45239</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>44964</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45015</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45610</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45159</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44880</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45169</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44897</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45967</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45841</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>44753</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45841</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44910</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45258</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45117</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45846</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45168</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45126</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45168</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>44712</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45793</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>45708</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44775</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45681</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45854</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44823</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45856</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>45750</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45741</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45488</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45257</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45733</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>45168</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45493</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45091</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>44917</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44917</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45099</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45001</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45797</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44817</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>45611</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44482</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45736</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45692</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>44879</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44879</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44917</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45267</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>45068</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>45159</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44699</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>44580</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>45642</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>45299</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>45311</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>44827</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44621</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45000</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45006</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45229</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45266</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45278</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45357</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>45581</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>45229</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>45579</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>45079</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>45750</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>45874</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>45581</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>45874</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29620,7 +29620,7 @@
         <v>45874</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>44917</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>45172</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>45082</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>45660</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>45660</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>45876</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45880</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45259</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>44830</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>45279</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>45168</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>45981</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44885</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>46105</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>46105</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>46105</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45264</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>44868</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>45154</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>46106</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>46107</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>45239</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>45239</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45386</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45450</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>45775</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>44845</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>45267</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>45329</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>46121</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>46121</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>46121</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>44482</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>45429</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>46128</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45268</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44875</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44595</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>46006</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>45404</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>45279</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44827</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>46008</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>46008</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45729</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>46007</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45257</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45727</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44806</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>44691</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>46013</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45071</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45692</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45973</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44482</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44482</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44964</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>44964</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45831</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>45408</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>46034</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>46031</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>45216</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>45168</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45826</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44713</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>45168</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45323</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44622</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45231</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45267</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44852</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>46050</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>44974</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45323</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>46057</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>46059</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>46059</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>46066</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>46066</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>46153</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>46079</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45895</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>45967</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45973</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>46105</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>46090</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>46162</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>46092</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>46162</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>45897</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>46162</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>46162</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>46168</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46167</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>46167</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>46167</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>46167</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>46034</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>45924</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>46173</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>46173</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>46176</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46178</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>46178</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>46176</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>46182</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>46181</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>46188</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>46189</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>46188</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>46188</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>46188</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>46188</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>46188</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>46188</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>46188</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>46188</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>46059</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>46188</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>46188</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>46196</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>46085</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>46205</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>46206</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>46210</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>46210</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45049</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>46210</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>46210</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>46210</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>46210</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>46210</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>46210</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>46265</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>46265</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>46265</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>46265</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>45677</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>46273</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>46274</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>46274</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>46260</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>46288</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>45988</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>46296</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>46296</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>46027</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>46253</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>46253</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>46254</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>46254</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>46259</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>46258</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>46259</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>46258</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>46258</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>46303</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46303</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>46276</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>46276</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>44132</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>44592</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>45516</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>44767</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>45171</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45672</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>45750</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45636</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45734</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42178,7 +42178,7 @@
         <v>45729</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>45716</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>46163</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>46212</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>46244</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>

--- a/Översikt HALMSTAD.xlsx
+++ b/Översikt HALMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45594</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>45099</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45447</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45820</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>44974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45442</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>45352</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>45352</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45730</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45168</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45168</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45168</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>44767</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45356</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45734</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45351</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45168</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44734</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>45168</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>46288</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45397</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45442</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44537</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44538</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>45168</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>45120</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45264</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45168</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>45042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>45894</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>46069</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>46175</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46153</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>44537</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>44537</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44656</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45306</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44715</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45035</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44482</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45883</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>45692</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45441</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44897</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45715</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>45168</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>45441</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45168</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>45168</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45812</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>45315</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>45154</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45839</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45615</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>45050</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>45082</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45029</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>44621</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>44699</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45874</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45692</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>46106</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>46057</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>46149</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>46162</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>46069</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>46176</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>45925</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>46178</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>46182</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>46057</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>46057</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>46300</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>45915</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>46141</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44756</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>44705</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>44677</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>44796</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>44873</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>44516</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>44537</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>44536</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>44760</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44538</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>44865</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>44593</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44538</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>44593</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>44628</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>44537</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44649</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>44677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>44579</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44760</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>44722</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>44494</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>44544</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>45632</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>44712</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>45050</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>45167</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45099</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45203</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44964</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45259</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>44775</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>45735</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45217</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>45168</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45168</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45169</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45275</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>45321</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45240</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>45168</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45561</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>45279</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45015</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45015</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44518</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45758</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45257</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44922</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45356</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44952</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45251</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45196</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>45265</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45230</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45335</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45883</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45316</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45562</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>45562</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45363</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44802</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45561</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45589</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45531</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>45065</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45306</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45259</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45079</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45537</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45800</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45750</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44886</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45800</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45769</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45805</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45714</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45712</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45170</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45168</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45258</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>44520</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>44557</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45680</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45476</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45476</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45894</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45485</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45488</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44537</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45329</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45734</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45358</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45740</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44885</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45415</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45607</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45561</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45194</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45699</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>44571</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45302</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45443</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45916</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44917</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>44610</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45555</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45156</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45630</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45170</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>45583</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44938</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45917</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45917</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>45555</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>45715</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45588</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45348</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45170</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44711</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45923</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45926</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>45792</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44594</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>44628</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>45747</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>45240</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>44687</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>45694</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>45627</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>45562</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>45632</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>44677</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45215</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45168</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>45316</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45716</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45931</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>45226</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45931</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44974</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>45589</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45797</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>45627</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>44642</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>45660</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44974</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45316</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45889</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>45681</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45681</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45091</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45090</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45938</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44607</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45330</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45006</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45735</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44742</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45217</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45217</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45359</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>44721</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>45168</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>45636</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45636</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45562</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45600</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45589</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45712</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45275</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>44662</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45401</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45817</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45260</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45099</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44722</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45642</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>44959</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45824</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45209</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45733</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>45183</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>45531</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45831</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>44742</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45831</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>45831</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45831</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45183</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45831</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45238</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45952</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45959</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45561</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45000</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45356</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45239</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>44964</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45015</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45610</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45159</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44880</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45169</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44897</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45967</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45841</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>44753</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45841</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44910</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45258</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45117</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45846</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45168</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45126</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45168</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>44712</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45793</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>45708</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44775</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45681</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45854</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44823</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45856</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>45750</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45741</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45488</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45257</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45733</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>45168</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45493</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45091</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>44917</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44917</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45099</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45001</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45797</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44817</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>45611</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44482</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45736</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45692</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>44879</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44879</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44917</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45267</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>45068</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>45159</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44699</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>44580</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>45642</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>45299</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>45311</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>44827</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44621</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45000</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45006</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45229</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45266</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45278</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45357</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>45581</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>45229</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>45579</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>45079</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>45750</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>45874</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>45581</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>45874</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29620,7 +29620,7 @@
         <v>45874</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>44917</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>45172</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>45082</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>45660</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>45660</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>45876</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45880</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45259</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>44830</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>45279</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>45168</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>45981</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44885</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>46105</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>46105</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>46105</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45264</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>44868</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>45154</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>46106</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>46107</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>45239</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>45239</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45386</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45450</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>45775</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>44845</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>45267</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>45329</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>46121</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>46121</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>46121</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>44482</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>45429</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>46128</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45268</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44875</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44595</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>46006</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>45404</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>45279</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44827</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>46008</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>46008</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45729</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>46007</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45257</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45727</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44806</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>44691</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>46013</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45071</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45692</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45973</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44482</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44482</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44964</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>44964</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45831</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>45408</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>46034</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>46031</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>45216</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>45168</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45826</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44713</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>45168</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45323</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44622</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45231</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45267</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44852</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>46050</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>44974</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45323</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>46057</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>46059</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>46059</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>46066</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>46066</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>46153</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>46079</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45895</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>45967</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45973</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>46105</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>46090</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>46162</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>46092</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>46162</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>45897</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>46162</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>46162</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>46168</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46167</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>46167</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>46167</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>46167</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>46034</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>45924</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>46173</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>46173</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>46176</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46178</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>46178</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>46176</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>46182</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>46181</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>46188</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>46189</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>46188</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>46188</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>46188</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>46188</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>46188</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>46188</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>46188</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>46188</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>46059</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>46188</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>46188</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>46196</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>46085</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>46205</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>46206</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>46210</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>46210</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45049</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>46210</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>46210</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>46210</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>46210</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>46210</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>46210</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>46265</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>46265</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>46265</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>46265</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>45677</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>46273</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>46274</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>46274</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>46260</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>46288</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>45988</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>46296</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>46296</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>46027</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>46253</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>46253</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>46254</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>46254</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>46259</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>46258</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>46259</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>46258</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>46258</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>46303</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46303</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>46276</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>46276</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>44132</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>44592</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>45516</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>44767</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>45171</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45672</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>45750</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45636</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45734</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42178,7 +42178,7 @@
         <v>45729</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>45716</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>46163</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>46212</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>46244</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>

--- a/Översikt HALMSTAD.xlsx
+++ b/Översikt HALMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45594</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>45099</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45447</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45820</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>44974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45442</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>45352</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>45352</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45730</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45168</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44767</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45168</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45168</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45356</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45734</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45351</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45168</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>45168</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>46288</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45397</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45442</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>45120</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>45168</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45894</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>46175</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>46069</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45042</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>45264</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>45168</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46153</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>44537</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>44537</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44656</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>44897</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>45306</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45168</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45315</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45168</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>45715</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>46149</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>46069</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>46162</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>45692</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45035</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>44715</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45441</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>45154</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>46176</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>46178</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>45925</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>46182</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>46057</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>46106</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>46057</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45168</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45441</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>46057</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>46300</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45812</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>45839</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>44621</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45692</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44699</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45082</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>45050</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>45029</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>45874</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45883</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>45915</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>46141</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>44756</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>44705</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44677</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>44796</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44711</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>44873</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>44516</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44537</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44536</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44872</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44538</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44593</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44649</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44760</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44760</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44677</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44865</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44538</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44537</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>44579</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>44722</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>44494</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>44593</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>44544</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>45279</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44875</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45079</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45363</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45630</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45610</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>45183</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>45358</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45091</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>45196</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45275</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45265</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>44845</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45240</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45733</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45169</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45168</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45660</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45775</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45561</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45168</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45168</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>45168</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>44823</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45734</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>45239</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44594</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>44691</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>44687</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45231</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45168</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45260</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44827</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45257</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45302</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>45065</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45000</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45356</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>45259</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45680</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>45015</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45015</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45015</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>45168</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>44885</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44885</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45275</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>44622</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>44952</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45257</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>44742</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>45240</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45329</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45805</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45488</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>44830</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45415</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45323</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45692</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45800</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>45660</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45735</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45714</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45531</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>45831</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45800</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45750</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45769</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45883</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45729</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45894</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45251</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45681</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45681</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45401</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45740</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45257</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45408</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45356</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45316</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45215</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>45589</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45168</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45170</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45091</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45917</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45916</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45917</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44662</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44711</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45715</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45259</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45488</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45923</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45335</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45926</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45931</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45931</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45279</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>46153</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45889</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45938</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45562</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45562</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45636</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45636</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>46105</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>45952</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45555</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45183</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>45959</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45279</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45168</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45268</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>45897</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>45209</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45967</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>46162</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45050</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>45329</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>46162</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>46162</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>46162</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>44712</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>45264</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45258</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>46167</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>46167</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45981</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>46167</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>46167</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44628</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>44880</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44897</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45758</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>46168</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45727</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>44557</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45476</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45476</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45607</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>46173</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45924</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>46034</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>46006</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45217</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>45348</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>45699</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>46008</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>46007</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>46173</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45323</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>46008</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>44607</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>46013</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>44518</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>44520</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45117</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>45537</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>44610</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44753</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>46176</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>46176</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>44721</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>45973</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>44742</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>44959</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>46031</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45170</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>46034</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>46178</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46178</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45159</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>44802</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>46182</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45316</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>46050</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44595</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>46181</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>46057</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>46059</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>44917</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>46059</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45126</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>46066</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>46188</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>46188</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>46188</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>46188</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>46188</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>46066</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45259</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45589</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>46188</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>46188</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46188</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>46188</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>44852</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>45170</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>46188</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>46188</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>46079</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>45485</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45967</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45895</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45973</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44974</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>46059</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44775</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>46189</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>46090</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>44910</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>46092</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>44571</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27243,7 +27243,7 @@
         <v>45168</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>45588</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>46196</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>46106</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>46105</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>46105</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>46105</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>46107</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>45156</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44868</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44938</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45006</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45660</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>46121</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>46121</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45217</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45217</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>46121</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>45321</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45267</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28713,7 +28713,7 @@
         <v>45267</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>46128</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45562</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>46085</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>45627</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>45154</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45386</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44642</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44722</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>44537</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>44712</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>45230</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45239</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>45239</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45826</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>46205</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>46206</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>45589</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45049</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44806</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>46210</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>46210</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>46210</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>46210</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>46210</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>46210</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>46210</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>46210</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>45168</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45168</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>44922</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>44964</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44964</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>46273</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>45168</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>45531</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44713</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>46274</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>45677</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>46274</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45404</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>45600</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>44974</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>45632</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44964</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45169</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32106,7 +32106,7 @@
         <v>45203</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32179,7 +32179,7 @@
         <v>45168</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>45988</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>45099</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>45632</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45238</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>45099</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>44827</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>45561</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>45712</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>46288</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>46260</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>44974</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45450</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>45429</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>45306</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>45561</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>45216</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>44964</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>45733</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44775</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45090</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>46254</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>46254</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>45267</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>46296</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34009,7 +34009,7 @@
         <v>46253</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>46296</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>46253</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>45194</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>45229</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44886</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>45712</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45071</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>46258</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>45443</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>45583</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>45555</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>46303</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>46303</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>46258</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>46258</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         <v>46259</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35260,7 +35260,7 @@
         <v>46259</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45747</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45792</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>45694</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44677</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35625,7 +35625,7 @@
         <v>45226</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>45562</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45797</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45716</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45316</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45627</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>46276</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>46276</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>46265</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>46265</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>46265</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>46308</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45735</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45330</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45359</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>46311</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45817</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45642</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>46027</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45824</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45831</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45831</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45831</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>45831</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>45831</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>45561</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45841</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37674,7 +37674,7 @@
         <v>45841</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>45708</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45793</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>45846</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45681</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45854</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45856</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45750</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>45741</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45493</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>45172</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>44917</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38550,7 +38550,7 @@
         <v>44917</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45079</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>45000</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>44917</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45736</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45229</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>44879</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>44879</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39134,7 +39134,7 @@
         <v>44917</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45581</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>45082</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>45001</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>44580</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44817</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>45311</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39645,7 +39645,7 @@
         <v>45266</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39718,7 +39718,7 @@
         <v>45642</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>45692</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>45006</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>45278</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>45611</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40083,7 +40083,7 @@
         <v>45159</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>44621</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>45099</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45750</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45357</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>45797</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>44699</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45068</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40672,7 +40672,7 @@
         <v>45581</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>45579</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>45299</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>45874</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>45874</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45874</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>45876</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45880</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>44132</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>44767</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>44592</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45171</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45672</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>45516</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41704,7 +41704,7 @@
         <v>45750</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41777,7 +41777,7 @@
         <v>45636</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>45734</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>45729</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45716</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42069,7 +42069,7 @@
         <v>46163</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42142,7 +42142,7 @@
         <v>46212</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42215,7 +42215,7 @@
         <v>46244</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>

--- a/Översikt HALMSTAD.xlsx
+++ b/Översikt HALMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45594</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>45099</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45447</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45820</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>44974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45442</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>45352</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>45352</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45730</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45168</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44767</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45168</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45168</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45356</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45734</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45351</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45168</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>45168</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>46288</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45397</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45442</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>45120</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>45168</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45894</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>46175</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>46069</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45042</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>45264</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>45168</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46153</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>44537</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>44537</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44656</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>44897</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>45306</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45168</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45315</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45168</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>45715</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>46149</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>46069</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>46162</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>45692</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45035</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>44715</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45441</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>45154</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>46176</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>46178</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>45925</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>46182</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>46057</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>46106</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>46057</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45168</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45441</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>46057</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>46300</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45812</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>45839</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>44621</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45692</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44699</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45082</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>45050</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>45029</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>45874</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45883</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>45915</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>46141</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>44756</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>44705</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44677</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>44796</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44711</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>44873</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>44516</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44537</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44536</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44872</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44538</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44593</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44649</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44760</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44760</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44677</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44865</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44538</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44537</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>44579</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>44722</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>44494</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>44593</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>44544</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>45279</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44875</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45079</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45363</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45630</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45610</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>45183</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>45358</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45091</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>45196</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45275</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45265</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>44845</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45240</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45733</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45169</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45168</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45660</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45775</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45561</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45168</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45168</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>45168</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>44823</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45734</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>45239</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44594</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>44691</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>44687</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45231</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45168</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45260</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44827</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45257</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45302</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>45065</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45000</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45356</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>45259</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45680</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>45015</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45015</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45015</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>45168</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>44885</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44885</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45275</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>44622</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>44952</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45257</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>44742</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>45240</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45329</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45805</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45488</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>44830</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45415</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45323</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45692</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45800</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>45660</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45735</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45714</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45531</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>45831</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45800</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45750</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45769</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45883</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45729</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45894</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45251</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45681</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45681</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45401</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45740</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45257</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45408</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45356</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45316</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45215</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>45589</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45168</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45170</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45091</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45917</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45916</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45917</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44662</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44711</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45715</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45259</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45488</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45923</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45335</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45926</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45931</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45931</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45279</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>46153</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45889</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45938</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45562</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45562</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45636</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45636</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>46105</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>45952</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45555</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45183</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>45959</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45279</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45168</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45268</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>45897</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>45209</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45967</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>46162</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45050</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>45329</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>46162</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>46162</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>46162</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>44712</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>45264</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45258</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>46167</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>46167</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45981</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>46167</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>46167</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44628</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>44880</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44897</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45758</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>46168</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45727</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>44557</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45476</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45476</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45607</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>46173</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45924</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>46034</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>46006</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45217</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>45348</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>45699</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>46008</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>46007</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>46173</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45323</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>46008</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>44607</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>46013</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>44518</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>44520</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45117</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>45537</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>44610</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44753</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>46176</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>46176</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>44721</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>45973</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>44742</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>44959</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>46031</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45170</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>46034</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>46178</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46178</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45159</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>44802</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>46182</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45316</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>46050</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44595</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>46181</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>46057</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>46059</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>44917</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>46059</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45126</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>46066</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>46188</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>46188</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>46188</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>46188</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>46188</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>46066</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45259</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45589</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>46188</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>46188</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46188</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>46188</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>44852</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>45170</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>46188</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>46188</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>46079</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>45485</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45967</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45895</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45973</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44974</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>46059</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44775</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>46189</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>46090</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>44910</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>46092</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>44571</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27243,7 +27243,7 @@
         <v>45168</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>45588</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>46196</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>46106</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>46105</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>46105</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>46105</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>46107</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>45156</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44868</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44938</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45006</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45660</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>46121</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>46121</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45217</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45217</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>46121</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>45321</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45267</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28713,7 +28713,7 @@
         <v>45267</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>46128</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45562</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>46085</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>45627</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>45154</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45386</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44642</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44722</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>44537</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>44712</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>45230</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45239</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>45239</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45826</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>46205</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>46206</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>45589</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45049</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44806</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>46210</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>46210</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>46210</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>46210</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>46210</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>46210</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>46210</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>46210</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>45168</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45168</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>44922</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>44964</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44964</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>46273</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>45168</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>45531</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44713</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>46274</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>45677</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>46274</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45404</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>45600</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>44974</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>45632</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44964</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45169</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32106,7 +32106,7 @@
         <v>45203</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32179,7 +32179,7 @@
         <v>45168</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>45988</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>45099</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>45632</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45238</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>45099</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>44827</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>45561</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>45712</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>46288</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>46260</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>44974</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45450</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>45429</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>45306</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>45561</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>45216</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>44964</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>45733</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44775</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45090</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>46254</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>46254</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>45267</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>46296</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34009,7 +34009,7 @@
         <v>46253</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>46296</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>46253</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>45194</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>45229</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44886</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>45712</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45071</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>46258</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>45443</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>45583</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>45555</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>46303</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>46303</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>46258</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>46258</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         <v>46259</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35260,7 +35260,7 @@
         <v>46259</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45747</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45792</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>45694</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44677</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35625,7 +35625,7 @@
         <v>45226</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>45562</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45797</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45716</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45316</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45627</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>46276</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>46276</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>46265</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>46265</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>46265</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>46308</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45735</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45330</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45359</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>46311</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45817</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45642</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>46027</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45824</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45831</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45831</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45831</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>45831</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>45831</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>45561</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45841</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37674,7 +37674,7 @@
         <v>45841</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>45708</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45793</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>45846</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45681</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45854</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45856</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45750</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>45741</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45493</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>45172</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>44917</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38550,7 +38550,7 @@
         <v>44917</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45079</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>45000</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>44917</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45736</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45229</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>44879</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>44879</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39134,7 +39134,7 @@
         <v>44917</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45581</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>45082</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>45001</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>44580</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44817</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>45311</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39645,7 +39645,7 @@
         <v>45266</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39718,7 +39718,7 @@
         <v>45642</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>45692</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>45006</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>45278</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>45611</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40083,7 +40083,7 @@
         <v>45159</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>44621</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>45099</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45750</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45357</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>45797</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>44699</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45068</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40672,7 +40672,7 @@
         <v>45581</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>45579</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>45299</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>45874</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>45874</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45874</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>45876</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45880</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>44132</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>44767</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>44592</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45171</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45672</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>45516</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41704,7 +41704,7 @@
         <v>45750</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41777,7 +41777,7 @@
         <v>45636</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>45734</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>45729</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45716</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42069,7 +42069,7 @@
         <v>46163</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42142,7 +42142,7 @@
         <v>46212</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42215,7 +42215,7 @@
         <v>46244</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>

--- a/Översikt HALMSTAD.xlsx
+++ b/Översikt HALMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45594</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>45099</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45447</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45820</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>45251</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44974</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45442</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>45352</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>45352</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45730</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>44767</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>45168</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45168</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45168</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45356</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45734</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45168</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44734</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>46288</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>45168</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45397</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45442</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>46175</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>45168</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45894</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>46069</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45120</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45168</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45264</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>45042</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46153</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>44537</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>44537</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44656</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45883</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>46162</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>46069</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45715</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>46176</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45925</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>46178</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>46182</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>45306</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44715</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>46057</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45692</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45441</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>46057</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45812</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>46057</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>45839</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>46300</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>46106</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45050</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>45082</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>45029</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44699</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>45874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>45692</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>44897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45441</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>46149</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>45168</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45168</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>45315</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>45615</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>45035</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45168</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45154</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>45915</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>46141</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>46314</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44756</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44705</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>44677</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44796</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>44873</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44516</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44537</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44536</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44593</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>44628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>44649</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44760</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>44760</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>44677</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44865</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>44538</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44537</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>44579</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>44722</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>44494</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>44593</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44875</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44595</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>44544</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45800</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45750</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45800</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45404</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45279</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44827</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45769</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45805</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44775</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45714</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>45735</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45217</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>45257</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44922</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>45727</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>44806</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>44691</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>45230</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>45071</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>45740</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>46162</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>46162</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45897</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>44964</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>44964</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>46162</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>46162</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45408</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45216</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45916</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45168</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>45917</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>44713</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>46168</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>45715</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>46167</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45168</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>46167</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45923</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>46167</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45926</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>46167</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44622</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>46034</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>45924</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>45931</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45931</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>45231</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>45267</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44852</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>45889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45938</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>44974</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>46173</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>45323</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>46173</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>45632</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>45259</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>44712</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>46176</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>45050</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>46178</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>46178</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45321</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45099</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>46176</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>44952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>44964</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>45168</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45168</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>46182</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>46181</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45952</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45169</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45240</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45168</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>45279</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>45959</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>46188</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>46189</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>46188</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>46188</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>45265</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46188</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>46188</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>46188</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>46188</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>46188</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>46188</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>46059</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>46188</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>46188</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45251</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45196</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45967</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45335</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45316</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45562</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45562</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45589</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>46196</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45065</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>46085</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45079</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44802</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>46205</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45168</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45712</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45981</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45170</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>45258</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44520</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45680</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>45531</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>46206</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>46210</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>46210</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45329</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45734</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45049</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>46210</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>46210</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>46210</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>46210</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45358</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>46210</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>46210</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45306</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45415</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45607</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>46006</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45677</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>46008</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45443</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>46008</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>46007</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>45555</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>45583</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>46013</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45973</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45792</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>46034</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>46031</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>45747</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>45694</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45627</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45562</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44677</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45537</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45316</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45716</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>45226</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>46260</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>46288</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>45797</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45988</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>46050</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45330</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44886</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45735</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>46057</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45359</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>46059</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>46059</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>46066</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>46066</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45817</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45642</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>46296</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>46296</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>45824</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>46253</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>46253</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>46079</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>45895</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45967</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>45831</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45831</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45831</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45831</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45973</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>46254</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45831</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>45561</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45168</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>46090</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>46092</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>46254</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45841</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45841</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45476</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45476</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45846</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>46105</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>46105</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>46105</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45793</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>46259</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>45485</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>45708</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>46258</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45488</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>46106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45681</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>46107</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45854</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44537</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45856</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>45750</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45741</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>46259</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>46258</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>46258</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>46303</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>45493</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>44885</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>46121</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44917</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>44917</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>46121</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>46121</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45099</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45001</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>45797</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>46303</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>46276</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>44817</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45611</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45736</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45692</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44879</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>44879</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>44917</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45068</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45159</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44699</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>44580</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45642</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>45299</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45311</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>44621</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>45000</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45006</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45229</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45266</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45278</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45357</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45581</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45579</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>45079</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45750</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45874</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45581</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>45874</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45874</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>44917</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>45172</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45082</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45876</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>46265</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>46265</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>46265</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45880</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>46128</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45561</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45883</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45194</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45699</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>44571</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>46265</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
         <v>45729</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>44917</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44610</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>44938</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45692</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>46311</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>45831</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>46027</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>44711</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45826</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45323</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>45240</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>44687</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>46273</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45215</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>46276</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>46317</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32803,7 +32803,7 @@
         <v>44974</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>46308</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32949,7 +32949,7 @@
         <v>45589</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33022,7 +33022,7 @@
         <v>46274</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>45627</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>46274</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>44642</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33314,7 +33314,7 @@
         <v>44974</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33387,7 +33387,7 @@
         <v>45090</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>44607</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45006</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>44742</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45168</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>46153</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45562</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45600</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>45589</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45712</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>46105</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>45275</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45260</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>44959</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45000</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45356</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>44964</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>45015</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>45610</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45159</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44880</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>44897</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44753</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45117</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45168</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>45168</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44775</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44823</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45488</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45733</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>45168</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45091</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44827</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>45229</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>45660</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>45660</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>44885</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45264</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>45154</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45775</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>44845</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45167</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45203</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>45275</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>45561</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45015</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45015</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>44518</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45758</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45257</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45356</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45363</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45561</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>45259</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>44557</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45302</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45156</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>45630</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45170</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45555</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45588</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45348</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>45170</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>44594</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>44628</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>45632</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38255,7 +38255,7 @@
         <v>45168</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>45660</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45316</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>45681</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45681</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45091</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>45217</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38781,7 +38781,7 @@
         <v>45217</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44721</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45636</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45636</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>44662</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45401</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45099</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>44722</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45209</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45733</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45183</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45531</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>44742</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45183</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45238</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45239</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45169</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>44910</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45258</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45126</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>44712</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45257</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45267</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45259</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>44830</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45279</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>45168</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44868</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>45239</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45239</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>45386</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45450</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>45267</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45329</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>45429</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>45268</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44132</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>44592</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>45516</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44767</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>45171</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41809,7 +41809,7 @@
         <v>45672</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45750</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>45636</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>45734</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>45729</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>45716</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>46163</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46212</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>46244</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>

--- a/Översikt HALMSTAD.xlsx
+++ b/Översikt HALMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45594</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>45099</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45447</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45820</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>45251</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44974</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45442</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>45352</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>45352</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45730</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>44767</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>45168</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45168</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45168</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45356</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45734</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45168</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44734</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>46288</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>45168</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45397</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45442</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44538</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>46175</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>45168</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45894</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>46069</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45120</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45168</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45264</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>45042</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46153</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>44537</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>44537</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44656</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45883</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>46162</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>46069</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45715</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>46176</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45925</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>46178</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>46182</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>45306</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44715</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>46057</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45692</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45441</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>46057</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45812</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>46057</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>45839</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>46300</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>46106</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45050</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>45082</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>45029</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44699</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>45874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>45692</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>44897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45441</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>46149</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>45168</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45168</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>45315</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>45615</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>45035</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45168</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45154</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>45915</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>46141</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>46314</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44756</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44705</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>44677</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44796</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>44873</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44516</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44537</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44536</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44593</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>44628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>44649</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44760</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>44760</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>44677</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44865</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>44538</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44537</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>44579</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>44722</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>44494</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>44593</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44875</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44595</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>44544</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45800</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45750</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45800</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45404</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45279</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44827</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45769</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45805</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44775</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45714</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>45735</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45217</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>45257</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44922</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>45727</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>44806</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>44691</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>45230</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>45071</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>45740</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>46162</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>46162</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45897</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>44964</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>44964</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>46162</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>46162</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45408</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45216</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45916</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45168</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>45917</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>44713</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>46168</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>45715</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>46167</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45168</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>46167</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45923</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>46167</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45926</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>46167</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44622</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>46034</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>45924</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>45931</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45931</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>45231</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>45267</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44852</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>45889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45938</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>44974</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>46173</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>45323</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>46173</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>45632</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>45259</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>44712</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>46176</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>45050</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>46178</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>46178</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45321</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45099</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>46176</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>44952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>44964</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>45168</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45168</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>46182</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>46181</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45952</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45169</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45240</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45168</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>45279</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>45959</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>46188</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>46189</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>46188</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>46188</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>45265</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46188</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>46188</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>46188</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>46188</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>46188</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>46188</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>46059</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>46188</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>46188</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45251</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45196</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45967</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45335</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45316</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45562</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45562</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45589</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>46196</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45065</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>46085</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45079</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44802</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>46205</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45168</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45712</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45981</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45170</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>45258</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44520</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45680</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>45531</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>46206</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>46210</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>46210</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45329</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45734</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45049</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>46210</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>46210</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>46210</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>46210</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45358</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>46210</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>46210</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45306</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45415</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45607</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>46006</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45677</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>46008</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45443</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>46008</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>46007</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>45555</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>45583</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>46013</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45973</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45792</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>46034</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>46031</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>45747</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>45694</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45627</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45562</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44677</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45537</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45316</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45716</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>45226</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>46260</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>46288</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>45797</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45988</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>46050</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45330</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44886</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45735</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>46057</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45359</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>46059</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>46059</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>46066</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>46066</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45817</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45642</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>46296</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>46296</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>45824</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>46253</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>46253</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>46079</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>45895</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45967</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>45831</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45831</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45831</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45831</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45973</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>46254</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45831</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>45561</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45168</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>46090</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>46092</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>46254</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45841</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45841</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45476</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45476</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45846</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>46105</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>46105</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>46105</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45793</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>46259</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>45485</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>45708</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>46258</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45488</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>46106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45681</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>46107</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45854</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44537</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45856</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>45750</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45741</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>46259</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>46258</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>46258</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>46303</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>45493</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>44885</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>46121</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44917</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>44917</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>46121</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>46121</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45099</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45001</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>45797</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>46303</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>46276</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>44817</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45611</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45736</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45692</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44879</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>44879</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>44917</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45068</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45159</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44699</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>44580</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45642</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>45299</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45311</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>44621</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>45000</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45006</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45229</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45266</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45278</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45357</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45581</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45579</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>45079</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45750</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45874</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45581</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>45874</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45874</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>44917</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>45172</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45082</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45876</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>46265</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>46265</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>46265</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45880</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>46128</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45561</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45883</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45194</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45699</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>44571</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>46265</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
         <v>45729</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>44917</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44610</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>44938</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45692</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>46311</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>45831</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>46027</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>44711</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45826</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45323</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>45240</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>44687</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>46273</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45215</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>46276</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>46317</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32803,7 +32803,7 @@
         <v>44974</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>46308</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32949,7 +32949,7 @@
         <v>45589</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33022,7 +33022,7 @@
         <v>46274</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>45627</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>46274</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>44642</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33314,7 +33314,7 @@
         <v>44974</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33387,7 +33387,7 @@
         <v>45090</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>44607</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45006</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>44742</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45168</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>46153</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45562</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45600</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>45589</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45712</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>46105</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>45275</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45260</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>44959</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45000</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45356</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>44964</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>45015</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>45610</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45159</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44880</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>44897</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44753</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45117</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45168</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>45168</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44775</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44823</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45488</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45733</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>45168</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45091</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44827</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>45229</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>45660</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>45660</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>44885</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45264</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>45154</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45775</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>44845</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45167</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45203</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>45275</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>45561</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45015</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45015</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>44518</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45758</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45257</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45356</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45363</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45561</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>45259</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>44557</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45302</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45156</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>45630</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45170</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45555</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45588</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45348</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>45170</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>44594</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>44628</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>45632</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38255,7 +38255,7 @@
         <v>45168</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>45660</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45316</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>45681</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45681</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45091</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>45217</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38781,7 +38781,7 @@
         <v>45217</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44721</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45636</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45636</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>44662</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45401</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45099</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>44722</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45209</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45733</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45183</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45531</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>44742</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45183</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45238</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45239</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45169</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>44910</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45258</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45126</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>44712</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45257</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45267</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45259</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>44830</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45279</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>45168</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44868</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>45239</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45239</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>45386</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45450</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>45267</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45329</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>45429</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>45268</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44132</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>44592</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>45516</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44767</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>45171</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41809,7 +41809,7 @@
         <v>45672</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45750</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>45636</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>45734</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>45729</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>45716</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>46163</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46212</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>46244</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
